--- a/data/config/companies.xlsx
+++ b/data/config/companies.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="123" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE7852A-3465-4864-ACF1-812228058754}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90719400-1D80-4AE8-BED6-9D0472DFDECE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" s="4">
         <v>1</v>
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" s="4">
         <v>1</v>
@@ -42087,15 +42087,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
@@ -42104,6 +42095,15 @@
     <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42296,11 +42296,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/config/companies.xlsx
+++ b/data/config/companies.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5337814B-9B79-4CFE-AAE6-1D45EA1B80B7}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6B6D0F7-70FE-41C2-BBA8-0842D6CB9A21}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="4">
         <v>1</v>
@@ -3633,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="4">
         <v>1</v>
@@ -3979,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="U19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="4">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="S23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="4">
         <v>0</v>
@@ -5365,7 +5365,7 @@
       <c r="U27" s="6">
         <v>0</v>
       </c>
-      <c r="V27" s="6">
+      <c r="V27" s="21">
         <v>0</v>
       </c>
       <c r="W27" s="6">
@@ -43080,17 +43080,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -43099,7 +43088,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000848DB8A027FFA44ADDDDBDD228782A6" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8d263d3cb1aa621d48e646d806cb1ef0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1dac145f-12f1-46c0-a8b8-4af8e41b8063" xmlns:ns3="00faf2f7-0679-4d56-a567-48d6a88ebe50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39e3593994817990d12a8ed679fcbd25" ns2:_="" ns3:_="">
     <xsd:import namespace="1dac145f-12f1-46c0-a8b8-4af8e41b8063"/>
@@ -43288,14 +43277,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57EBF12A-D63D-4216-8486-79A07EF61A2B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57EBF12A-D63D-4216-8486-79A07EF61A2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
 </file>
--- a/data/config/companies.xlsx
+++ b/data/config/companies.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6B6D0F7-70FE-41C2-BBA8-0842D6CB9A21}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86303B5C-3173-4F48-8603-3434E28CF40A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -415,7 +415,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -437,6 +437,13 @@
       <u/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -527,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -558,6 +565,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2323,7 +2331,7 @@
       <c r="AS9">
         <v>1</v>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="24">
         <v>1</v>
       </c>
       <c r="AU9">
@@ -3883,7 +3891,7 @@
       <c r="AT18">
         <v>0</v>
       </c>
-      <c r="AU18">
+      <c r="AU18" s="24">
         <v>0</v>
       </c>
       <c r="AV18">
@@ -43080,12 +43088,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -43278,18 +43288,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -43297,5 +43305,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
 </file>
--- a/data/config/companies.xlsx
+++ b/data/config/companies.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86303B5C-3173-4F48-8603-3434E28CF40A}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="11_1A3613343B44BEDA63B0D64456CF9F90A93B660E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24ADE55F-2ABB-4121-976D-C6F9FAA7AAE5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="128">
   <si>
     <t>id_invgate</t>
   </si>
@@ -408,7 +408,13 @@
     <t>Prune</t>
   </si>
   <si>
-    <t>PRN</t>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>Farmapay</t>
+  </si>
+  <si>
+    <t>FMP</t>
   </si>
 </sst>
 </file>
@@ -4229,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="AR20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS20">
         <v>1</v>
@@ -7177,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV37">
         <v>0</v>
@@ -7192,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA37">
         <v>0</v>
@@ -7212,41 +7218,174 @@
     </row>
     <row r="38" spans="1:57" ht="12.75">
       <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6"/>
-      <c r="AA38" s="6"/>
-      <c r="AB38" s="6"/>
-      <c r="AC38" s="6"/>
-      <c r="AD38" s="6"/>
-      <c r="AE38" s="6"/>
-      <c r="AF38" s="6"/>
-      <c r="AG38" s="6"/>
-      <c r="AH38" s="6"/>
-      <c r="AI38" s="6"/>
-      <c r="AJ38" s="6"/>
+      <c r="B38" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="6">
+        <v>1</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>0</v>
+      </c>
+      <c r="R38" s="6">
+        <v>0</v>
+      </c>
+      <c r="S38" s="6">
+        <v>0</v>
+      </c>
+      <c r="T38" s="6">
+        <v>0</v>
+      </c>
+      <c r="U38" s="6">
+        <v>0</v>
+      </c>
+      <c r="V38" s="6">
+        <v>0</v>
+      </c>
+      <c r="W38" s="6">
+        <v>0</v>
+      </c>
+      <c r="X38" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>1</v>
+      </c>
+      <c r="AV38">
+        <v>1</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>1</v>
+      </c>
+      <c r="AY38">
+        <v>1</v>
+      </c>
+      <c r="AZ38">
+        <v>1</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="1:57" ht="12.75">
       <c r="A39" s="3"/>
@@ -7361,6 +7500,7 @@
       <c r="AH41" s="4"/>
       <c r="AI41" s="4"/>
       <c r="AJ41" s="4"/>
+      <c r="AX41" s="24"/>
     </row>
     <row r="42" spans="1:57" ht="12.75">
       <c r="A42" s="5"/>
@@ -43088,17 +43228,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000848DB8A027FFA44ADDDDBDD228782A6" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8d263d3cb1aa621d48e646d806cb1ef0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1dac145f-12f1-46c0-a8b8-4af8e41b8063" xmlns:ns3="00faf2f7-0679-4d56-a567-48d6a88ebe50" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39e3593994817990d12a8ed679fcbd25" ns2:_="" ns3:_="">
     <xsd:import namespace="1dac145f-12f1-46c0-a8b8-4af8e41b8063"/>
@@ -43287,7 +43416,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -43296,14 +43425,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1dac145f-12f1-46c0-a8b8-4af8e41b8063">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="00faf2f7-0679-4d56-a567-48d6a88ebe50" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57EBF12A-D63D-4216-8486-79A07EF61A2B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57EBF12A-D63D-4216-8486-79A07EF61A2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D628AF90-3961-4293-BFE0-65CFEABA0C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CC45C34-22F2-40A6-BF97-316903A7791D}"/>
 </file>